--- a/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
+++ b/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
@@ -1826,7 +1826,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>broken</t>
+          <t>disconnected</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated. The report places Malani at Chopdiyal Gaon (field GPS: Gunogi), so its row may belong to Nimbujhard.</t>
+          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated. The report prints Chopdiyal Gaon as the village; Malani is at Gunogi (report error, confirmed by Rajat).</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated. The report places Nimbujhard at Gunogi (field GPS: Chopriyal), so its row may belong to Malani.</t>
+          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated. The report prints Gunogi as the village; Nimbujhard is at Chopriyal 2 (report error, confirmed by Rajat).</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>

--- a/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
+++ b/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8 DI springs from the WATSAN Spring Assessment Report and the SRHU reports, plus Paniyar Dhar (no DI) as a comparison spring next to Balench. Kokhliyal is a Himmotthan site without DI, so it is not included.</t>
+          <t>9 DI springs from the WATSAN Spring Assessment Report and the SRHU reports. Arakot 2 may feed both Balench and Paniyar Dhar, so it is listed under both; count its water once. Kokhliyal is a Himmotthan site without DI, so it is not included.</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Comparison spring (no DI)</t>
+          <t>DI site</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1285,10 +1285,14 @@
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>FV26-DI-ARK2</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>No DI feeds it directly; Arakot 2 is nearest but not established (Rajat 2026-10-22)</t>
+          <t>Arakot 2 may feed Paniyar Dhar as well as Balench (Rajat, 2026-10-24); not verified</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1608,7 +1612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2413,12 +2417,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FV26-DI-KAN</t>
+          <t>FV26-DI-ARK2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WDI-07</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2428,33 +2432,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kanatal</t>
+          <t>Arakot 2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30.419538</t>
+          <t>30.365313</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>78.325791</t>
+          <t>78.379288</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2407.8</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
+          <t>1796.6</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>99</v>
+      </c>
+      <c r="I8" t="n">
+        <v>258</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -2462,9 +2462,13 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>200</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>150</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Form gives 300 m2 for Arakot 1 and 2 together; split evenly</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>Concrete</t>
@@ -2482,14 +2486,10 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>not_checked</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -2500,12 +2500,12 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>reported, not verified</t>
+          <t>reported, not verified; nearest DI to Paniyar Dhar but link to it not established</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -2515,19 +2515,19 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Working; Roadside, heavy litter; safety flag: clogging/dirty inflow; Depth on the form 100 m, reduced by 30 m (Rajat 2026-10-23: form depths were recorded about 30 m high)</t>
+          <t>Pump condition not recorded; Tested during visit; Depth on the form 100 m, reduced by 30 m (Rajat 2026-10-23: form depths were recorded about 30 m high)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FV26-DI-KUN</t>
+          <t>FV26-DI-KAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WDI-08</t>
+          <t>WDI-07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2537,51 +2537,65 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kunjapuri</t>
+          <t>Kanatal</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30.173165</t>
+          <t>30.419538</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>78.313007</t>
+          <t>78.325791</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1559.6</t>
+          <t>2407.8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>152</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>200</v>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Concrete</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>not_checked</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="S9" t="inlineStr">
         <is>
           <t>working</t>
@@ -2595,12 +2609,12 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Reported by WATSAN/SRHU report; spring not seen on the visit (water tapped directly)</t>
+          <t>reported, not verified</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -2610,19 +2624,19 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Water tapped directly from the handpump; Working (recent DI on a previously defunct handpump); Exposed plastic roof pipes; animal and monkey damage risk</t>
+          <t>Working; Roadside, heavy litter; safety flag: clogging/dirty inflow; Depth on the form 100 m, reduced by 30 m (Rajat 2026-10-23: form depths were recorded about 30 m high)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SRC028-DI-DUN</t>
+          <t>FV26-DI-KUN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WDI-09</t>
+          <t>WDI-08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2632,42 +2646,137 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Dungsi (Domsi)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>30.481472</v>
-      </c>
-      <c r="F10" t="n">
-        <v>78.236694</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>Kunjapuri</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>30.173165</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>78.313007</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1559.6</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>not_checked</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>not_checked</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>working</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>connected</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Reported by WATSAN/SRHU report; spring not seen on the visit (water tapped directly)</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Water tapped directly from the handpump; Working (recent DI on a previously defunct handpump); Exposed plastic roof pipes; animal and monkey damage risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SRC028-DI-DUN</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>WDI-09</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Dungsi (Domsi)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>30.481472</v>
+      </c>
+      <c r="F11" t="n">
+        <v>78.236694</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>Reported by the SRHU Dungsi &amp; Makhdet report (SRC-028); not visited</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SRHU Dungsi &amp; Makhdet hydrogeology report (SRC-028); handpump printed as 30°28'53.3"N 78°14'12.1"E</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2680,7 +2789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P68"/>
+  <dimension ref="A1:P70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6271,7 +6380,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>No DI. People said the flow has stayed similar: it dries every summer.</t>
+          <t>People said the flow has stayed similar: it still dries every summer.</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
@@ -6341,7 +6450,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>No DI. People said the flow has stayed similar: it dries every summer.</t>
+          <t>People said the flow has stayed similar: it still dries every summer.</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
@@ -6360,12 +6469,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>village</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>WDI-06</t>
+          <t>FV26-DI-ARK2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6385,19 +6494,19 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>village_change</t>
+          <t>pump_status</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Still dries every summer</t>
+          <t>not_checked</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>observed</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6407,19 +6516,11 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Dries in lean months; people fetch water from Balench | No DI here: comparison spring.</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>access</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
+          <t>Pump condition not recorded</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6429,17 +6530,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WDI-07</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>RDI-SPR-0007</t>
+          <t>FV26-DI-ARK2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6459,14 +6560,14 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>~16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6481,7 +6582,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated.</t>
+          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
@@ -6495,17 +6596,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WDI-07</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>village</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>RDI-SPR-0007</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6520,28 +6621,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
-        </is>
-      </c>
-      <c r="I57" t="n">
-        <v>21.72</v>
-      </c>
-      <c r="J57" t="n">
-        <v>21.72</v>
-      </c>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2 L in 5.8 s; 2 L in 5.5 s; 2 L in 5.3 s</t>
+          <t>Still dries every summer</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6551,11 +6648,19 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Mean of 3 bucket-and-stopwatch readings, whole flow caught at the outlet pipe.</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
+          <t>Dries in lean months; people fetch water from Balench | Arakot 2 DI may feed this spring; no change reported.</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6580,7 +6685,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6588,40 +6693,36 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
+          <t>flow_lpm</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>10-15 L/min</t>
+          <t>~16</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Typical flow people gave for this season now.</t>
+          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated.</t>
         </is>
       </c>
       <c r="O58" t="inlineStr"/>
@@ -6665,23 +6766,23 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>monsoon_flow_lpm</t>
+          <t>flow_lpm</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>21.72</v>
       </c>
       <c r="J59" t="n">
-        <v>25</v>
+        <v>21.72</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>20-25 L/min</t>
+          <t>2 L in 5.8 s; 2 L in 5.5 s; 2 L in 5.3 s</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6691,7 +6792,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Typical flow people gave for this season now.</t>
+          <t>Mean of 3 bucket-and-stopwatch readings, whole flow caught at the outlet pipe.</t>
         </is>
       </c>
       <c r="O59" t="inlineStr"/>
@@ -6735,14 +6836,18 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>reported_change</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>lean_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>10</v>
+      </c>
+      <c r="J60" t="n">
+        <v>15</v>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>increase</t>
+          <t>10-15 L/min</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6757,7 +6862,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Flow compared with 10-20 years ago: More. Nearby houses use this spring; flow has increased</t>
+          <t>Typical flow people gave for this season now.</t>
         </is>
       </c>
       <c r="O60" t="inlineStr"/>
@@ -6776,35 +6881,43 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FV26-DI-KAN</t>
+          <t>RDI-SPR-0007</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>before_di_recall</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>before_di</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>monsoon_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>20</v>
+      </c>
+      <c r="J61" t="n">
+        <v>25</v>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>no_water_dry_season</t>
+          <t>20-25 L/min</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6814,12 +6927,12 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026 (recalled on 2026-10-19)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Handpump has water in the dry season now (implies it did not before)</t>
+          <t>Typical flow people gave for this season now.</t>
         </is>
       </c>
       <c r="O61" t="inlineStr"/>
@@ -6838,12 +6951,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FV26-DI-KAN</t>
+          <t>RDI-SPR-0007</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6863,19 +6976,19 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>pump_status</t>
+          <t>reported_change</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>increase</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>observed</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6883,7 +6996,11 @@
           <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Flow compared with 10-20 years ago: More. Nearby houses use this spring; flow has increased</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
     </row>
@@ -6910,44 +7027,40 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>before_di_recall</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>after_di</t>
+          <t>before_di</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
-        </is>
-      </c>
-      <c r="I63" t="n">
-        <v>16</v>
-      </c>
-      <c r="J63" t="n">
-        <v>16</v>
-      </c>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>no_water_dry_season</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026 (recalled on 2026-10-19)</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
+          <t>Handpump has water in the dry season now (implies it did not before)</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
@@ -6991,19 +7104,19 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>village_change</t>
+          <t>pump_status</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Has water in the dry season; very good quality, travellers drink and wash</t>
+          <t>working</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>observed</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7011,21 +7124,9 @@
           <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Handpump had no water in the dry season</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>access</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7040,17 +7141,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>RDI-SPR-0007</t>
+          <t>FV26-DI-KAN</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7058,48 +7159,40 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>village_change</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>16</v>
+      </c>
+      <c r="J65" t="n">
+        <v>16</v>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Flow has increased</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Lower spring flow</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>access</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
+          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7109,7 +7202,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WDI-08</t>
+          <t>WDI-07</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7119,30 +7212,34 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>FV26-DI-KUN</t>
+          <t>FV26-DI-KAN</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>before_di_recall</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>before_di</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>pump_status</t>
+          <t>village_change</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>defunct</t>
+          <t>Has water in the dry season; very good quality, travellers drink and wash</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -7152,16 +7249,24 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026 (recalled on 2026-10-21)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>DI was fitted on a previously defunct handpump</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
+          <t>Handpump had no water in the dry season</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7171,17 +7276,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WDI-08</t>
+          <t>WDI-07</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>FV26-DI-KUN</t>
+          <t>RDI-SPR-0007</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7196,24 +7301,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>pump_status</t>
+          <t>village_change</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>Flow has increased</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>observed</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7223,11 +7328,19 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Water tapped directly from the handpump</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
+          <t>Lower spring flow</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7252,52 +7365,180 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>before_di_recall</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>after_di</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>village_change</t>
+          <t>pump_status</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
+          <t>defunct</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Field form, DOCC/WATSAN field visit, October 2026 (recalled on 2026-10-21)</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>DI was fitted on a previously defunct handpump</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>OBS-068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>WDI-08</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>handpump</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>FV26-DI-KUN</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>field_visit_2026_10</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>working</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>observed</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Water tapped directly from the handpump</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>OBS-069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>WDI-08</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>handpump</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>FV26-DI-KUN</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>field_visit_2026_10</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
           <t>Handpump working; water tapped directly</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>Handpump defunct</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>access</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>better</t>
         </is>

--- a/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
+++ b/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>before_di = how things were before DI (recall only; no measured before-DI flow exists). after_di = any record taken after DI was fitted.</t>
+          <t>before_di = how things were before DI (agreed values; no measured before-DI flow exists). after_di = any record taken after DI was fitted.</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>before_di_recall = what people said on the field visit about the time before DI; watsan_report = WATSAN Spring Assessment Report values (undated, after DI); field_visit_2026_10 = DOCC/WATSAN field visit, 18-21 Oct 2026.</t>
+          <t>before_di_agreed = before-DI values agreed by Rajat on 2026-10-24 from the earlier RDI reports; watsan_report = WATSAN Spring Assessment Report values (undated, after DI); field_visit_2026_10 = DOCC/WATSAN field visit, 18-21 Oct 2026.</t>
         </is>
       </c>
     </row>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>measured = bucket and stopwatch; estimate = judged by eye; report = value printed in a report, method not stated; recall = what people said; observed = condition seen on the visit.</t>
+          <t>agreed = value agreed by Rajat (2026-10-24) from reports and field forms; measured = bucket and stopwatch; estimate = judged by eye; report = value printed in a report, method not stated; recall = what people said; observed = condition seen on the visit.</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Pump condition not ticked; delivery test 6-7 strokes for 1-2 L shows it gives water; Roof pipe broken; Exposed plastic roof pipe along the road; Depth on the form 100 m, reduced by 30 m (Rajat 2026-10-23: form depths were recorded about 30 m high)</t>
+          <t>Delivery test 6-7 strokes for 1-2 L; Roof pipe broken; Exposed plastic roof pipe along the road; Depth on the form 100 m, reduced by 30 m (Rajat 2026-10-23: form depths were recorded about 30 m high)</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>working</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Pump condition not recorded; Tested during visit; Depth on the form 100 m, reduced by 30 m (Rajat 2026-10-23: form depths were recorded about 30 m high)</t>
+          <t>Pump box not ticked on the form; Working (Rajat, 2026-10-24); Tested during visit; Depth on the form 100 m, reduced by 30 m (Rajat 2026-10-23: form depths were recorded about 30 m high)</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Uniyal Gaon, Kaddukhal (school handpump near Surkanda Devi)</t>
+          <t>Kaddukhal</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>broken</t>
+          <t>working</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Possible vehicle damage (not confirmed); Pump broken; Installed last year for the school; possible vehicle damage (not confirmed); Depth on the form 90 m, reduced by 30 m (Rajat 2026-10-23: form depths were recorded about 30 m high)</t>
+          <t>Field form recorded it broken (possible vehicle damage); Working (Rajat, 2026-10-24); Pump broken; Installed last year for the school; possible vehicle damage (not confirmed); Depth on the form 90 m, reduced by 30 m (Rajat 2026-10-23: form depths were recorded about 30 m high)</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>working</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Pump condition not recorded; people said it has water in the dry season now; Disconnected (house construction); Handpump was defunct with high-iron water before DI; reported improvement after DI (no lab results); Depth on the form 110 m, set to 40 m by Rajat (2026-10-23)</t>
+          <t>Pump box not ticked on the form; people said it has water in the dry season; Disconnected (house construction); Handpump was defunct with high-iron water before DI; reported improvement after DI (no lab results); Depth on the form 110 m, set to 40 m by Rajat (2026-10-23)</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>working</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Pump condition not recorded; Tested during visit; Depth on the form 100 m, reduced by 30 m (Rajat 2026-10-23: form depths were recorded about 30 m high)</t>
+          <t>Pump box not ticked on the form; Working (Rajat, 2026-10-24); Tested during visit; Depth on the form 100 m, reduced by 30 m (Rajat 2026-10-23: form depths were recorded about 30 m high)</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,11 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>working</t>
+        </is>
+      </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
@@ -2776,7 +2780,11 @@
           <t>SRHU Dungsi &amp; Makhdet hydrogeology report (SRC-028); handpump printed as 30°28'53.3"N 78°14'12.1"E</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Not visited; Working (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2789,7 +2797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P70"/>
+  <dimension ref="A1:P84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3033,44 +3041,44 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>after_di</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>reported_change</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>lean_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>increase</t>
+          <t>1.5 L/min</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flow compared with 10-20 years ago: More. </t>
+          <t>Dry-season flow before DI.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -3099,44 +3107,48 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>before_di_recall</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>before_di</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>lean_flow_lpm</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1-2 L/min</t>
+          <t>3 L/min</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026 (recalled on 2026-10-18)</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Guide: lean flow 1-2 L/min before DI, 2-3 L/min now. The form's lean-flow box says about 1 L/min, so the gain is uncertain.</t>
+          <t>Dry-season flow after DI.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -3180,33 +3192,33 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
+          <t>monsoon_flow_lpm</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2-3 L/min</t>
+          <t>8 L/min</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Guide: lean flow 1-2 L/min before DI, 2-3 L/min now. The form's lean-flow box says about 1 L/min, so the gain is uncertain.</t>
+          <t>Monsoon flow after DI.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -3225,35 +3237,39 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FV26-DI-ARK1</t>
+          <t>RDI-SPR-0001</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>before_di_recall</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>before_di</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>pump_status</t>
+          <t>reported_change</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>defunct</t>
+          <t>increase</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -3263,12 +3279,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026 (recalled on 2026-10-18)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Handpump was defunct before DI, now has water in the dry season (Balench form)</t>
+          <t xml:space="preserve">Flow compared with 10-20 years ago: More. </t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -3297,19 +3313,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>after_di</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>pump_status</t>
@@ -3319,22 +3331,22 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>defunct</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>observed</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Pump condition not ticked; delivery test 6-7 strokes for 1-2 L shows it gives water</t>
+          <t>Balench form: handpump was defunct before DI, now has water in the dry season</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -3378,29 +3390,29 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>pump_yield</t>
+          <t>pump_status</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6-7 strokes -&gt; 1-2 L</t>
+          <t>working</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>observed</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Strokes per litre; not convertible to L/min without timing.</t>
+          <t>Delivery test 6-7 strokes for 1-2 L</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -3429,7 +3441,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3437,36 +3449,36 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
+          <t>pump_yield</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6-7 strokes -&gt; 1-2 L</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>observed</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
+          <t>Strokes per litre; not convertible to L/min without timing.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -3490,12 +3502,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FV26-DI-ARK2</t>
+          <t>FV26-DI-ARK1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3503,36 +3515,36 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>observed</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Pump condition not recorded</t>
+          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -3556,61 +3568,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FV26-DI-ARK1</t>
+          <t>FV26-DI-ARK2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>after_di</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>village_change</t>
+          <t>pump_status</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Handpump has water in the dry season; water decent, slight iron</t>
+          <t>defunct</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Arakot handpump was defunct</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>access</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3620,22 +3616,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WDI-02</t>
+          <t>WDI-01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>RDI-SPR-0002</t>
+          <t>FV26-DI-ARK2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3643,36 +3639,36 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>12</v>
-      </c>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8–12</t>
+          <t>working</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated.</t>
+          <t>Pump box not ticked on the form; Working (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -3686,17 +3682,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WDI-02</t>
+          <t>WDI-01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>RDI-SPR-0002</t>
+          <t>FV26-DI-ARK1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3716,19 +3712,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
+          <t>village_change</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Could not measure, but perennial</t>
+          <t>Handpump has water in the dry season; water decent, slight iron</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>not_measured</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -3736,9 +3732,21 @@
           <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Arakot handpump was defunct</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3763,7 +3771,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3771,36 +3779,36 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>reported_change</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>12</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>increase</t>
+          <t>8–12</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Flow compared with 10-20 years ago: More. Entire village depends on the solar pumping project; before: severe water crisis, 2-3 km walk downhill; now water available, vegetation and farming</t>
+          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -3819,12 +3827,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FV26-DI-CHP1</t>
+          <t>RDI-SPR-0002</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3844,19 +3852,19 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>pump_status</t>
+          <t>flow_lpm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>Could not measure, but perennial</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>observed</t>
+          <t>not_measured</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -3881,54 +3889,54 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FV26-DI-CHP1</t>
+          <t>RDI-SPR-0002</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>after_di</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>pump_yield</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>lean_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>8</v>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7-8 strokes -&gt; 1-2 L</t>
+          <t>8 L/min</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>observed</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Strokes per litre; not convertible to L/min without timing.</t>
+          <t>Dry-season flow before DI.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -3947,17 +3955,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FV26-DI-CHP1</t>
+          <t>RDI-SPR-0002</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3965,10 +3973,14 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
+          <t>lean_flow_lpm</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -3979,22 +3991,22 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>12 L/min</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
+          <t>Dry-season flow after DI.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
@@ -4013,12 +4025,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>village</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>WDI-02</t>
+          <t>RDI-SPR-0002</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4038,41 +4050,37 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>village_change</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>monsoon_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>20</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Water available in the village; vegetation and farming</t>
+          <t>20 L/min</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Severe water crisis; people walked 2-3 km downhill for water | Himmotthan solar pumping from the spring is a separate scheme and explains much of this.</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>access</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
+          <t>Monsoon flow after DI.</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4082,7 +4090,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WDI-03</t>
+          <t>WDI-02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4092,12 +4100,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>RDI-SPR-0003</t>
+          <t>RDI-SPR-0002</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4105,36 +4113,36 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>8</v>
-      </c>
-      <c r="J20" t="n">
-        <v>15</v>
-      </c>
+          <t>reported_change</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8–15</t>
+          <t>increase</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated.</t>
+          <t>Flow compared with 10-20 years ago: More. Entire village depends on the solar pumping project; before: severe water crisis, 2-3 km walk downhill; now water available, vegetation and farming</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
@@ -4148,65 +4156,53 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WDI-03</t>
+          <t>WDI-02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>RDI-SPR-0003</t>
+          <t>FV26-DI-CHP1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>after_di</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3</v>
-      </c>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2-3 L/min (estimate from looking at the source)</t>
+          <t>defunct</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Estimated by looking at the source, not timed.</t>
-        </is>
-      </c>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
     </row>
@@ -4218,17 +4214,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WDI-03</t>
+          <t>WDI-02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>RDI-SPR-0003</t>
+          <t>FV26-DI-CHP1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4243,40 +4239,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2 L/min</t>
+          <t>working</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Typical flow people gave for this season now.</t>
-        </is>
-      </c>
+          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
     </row>
@@ -4288,17 +4276,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WDI-03</t>
+          <t>WDI-02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>RDI-SPR-0003</t>
+          <t>FV26-DI-CHP1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4313,28 +4301,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>monsoon_flow_lpm</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>7</v>
-      </c>
-      <c r="J23" t="n">
-        <v>8</v>
-      </c>
+          <t>pump_yield</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>7-8 L/min</t>
+          <t>7-8 strokes -&gt; 1-2 L</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>observed</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -4344,7 +4328,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Typical flow people gave for this season now.</t>
+          <t>Strokes per litre; not convertible to L/min without timing.</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -4358,22 +4342,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WDI-03</t>
+          <t>WDI-02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>RDI-SPR-0003</t>
+          <t>FV26-DI-CHP1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4381,36 +4365,36 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>reported_change</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>12</v>
+      </c>
+      <c r="J24" t="n">
+        <v>12</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Flow compared with 10-20 years ago: Same. Only source when JJM is not supplying; no impact from DI</t>
+          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -4424,17 +4408,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WDI-03</t>
+          <t>WDI-02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>village</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FV26-DI-UNI</t>
+          <t>WDI-02</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4449,24 +4433,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>pump_status</t>
+          <t>village_change</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>broken</t>
+          <t>Water available in the village; vegetation and farming</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>observed</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -4476,11 +4460,19 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Possible vehicle damage (not confirmed)</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+          <t>Severe water crisis; people walked 2-3 km downhill for water | Himmotthan solar pumping from the spring is a separate scheme and explains much of this.</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4495,12 +4487,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FV26-DI-UNI</t>
+          <t>RDI-SPR-0003</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4520,14 +4512,14 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J26" t="n">
         <v>15</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8–15</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -4542,7 +4534,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
+          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated.</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
@@ -4561,12 +4553,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>village</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>WDI-03</t>
+          <t>RDI-SPR-0003</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4586,19 +4578,23 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>village_change</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3</v>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>No impact from DI seen</t>
+          <t>2-3 L/min (estimate from looking at the source)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -4608,19 +4604,11 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Naula is the only source when JJM does not supply | Geologist found no link between the DI handpump and the naula.</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>access</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
+          <t>Estimated by looking at the source, not timed.</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4630,7 +4618,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WDI-04</t>
+          <t>WDI-03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4640,49 +4628,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>RDI-SPR-0004</t>
+          <t>RDI-SPR-0003</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>after_di</t>
+          <t>before_di</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
+          <t>lean_flow_lpm</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>7–9</t>
+          <t>3 L/min</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated. The report prints Chopdiyal Gaon as the village; Malani is at Gunogi (report error, confirmed by Rajat).</t>
+          <t>Dry-season flow before DI.</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
@@ -4696,7 +4684,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WDI-04</t>
+          <t>WDI-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4706,7 +4694,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>RDI-SPR-0004</t>
+          <t>RDI-SPR-0003</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4726,33 +4714,33 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
+          <t>lean_flow_lpm</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>17.09</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
-        <v>17.09</v>
+        <v>3</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2 L in 7.58 s; 2 L in 6.5 s; 2 L in 7.07 s</t>
+          <t>3 L/min</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Mean of 3 bucket-and-stopwatch readings, whole flow caught at the outlet pipe.</t>
+          <t>Dry-season flow after DI.</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
@@ -4766,7 +4754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WDI-04</t>
+          <t>WDI-03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4776,7 +4764,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>RDI-SPR-0004</t>
+          <t>RDI-SPR-0003</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4796,33 +4784,33 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
+          <t>monsoon_flow_lpm</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J30" t="n">
         <v>10</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>9-10 L/min</t>
+          <t>10 L/min</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Typical flow people gave for this season now.</t>
+          <t>Monsoon flow after DI.</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
@@ -4836,7 +4824,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>WDI-04</t>
+          <t>WDI-03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4846,7 +4834,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>RDI-SPR-0004</t>
+          <t>RDI-SPR-0003</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4866,18 +4854,14 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>monsoon_flow_lpm</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>17</v>
-      </c>
-      <c r="J31" t="n">
-        <v>20</v>
-      </c>
+          <t>reported_change</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>17-20 L/min</t>
+          <t>same</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -4892,7 +4876,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Typical flow people gave for this season now.</t>
+          <t>Flow compared with 10-20 years ago: Same. Only source when JJM is not supplying; no impact from DI</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
@@ -4906,61 +4890,53 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>WDI-04</t>
+          <t>WDI-03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>RDI-SPR-0004</t>
+          <t>FV26-DI-UNI</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>after_di</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>reported_change</t>
+          <t>pump_status</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>increase</t>
+          <t>defunct</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flow compared with 10-20 years ago: More. </t>
-        </is>
-      </c>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
     </row>
@@ -4972,7 +4948,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>WDI-04</t>
+          <t>WDI-03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4982,20 +4958,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FV26-DI-GUN</t>
+          <t>FV26-DI-UNI</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>before_di_recall</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>before_di</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>pump_status</t>
@@ -5005,22 +4985,22 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>poor_quality</t>
+          <t>working</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026 (recalled on 2026-10-19)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Handpump gave less water and had high iron before DI; flow has increased</t>
+          <t>Field form recorded it broken (possible vehicle damage); Working (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
@@ -5034,7 +5014,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>WDI-04</t>
+          <t>WDI-03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5044,12 +5024,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FV26-DI-GUN</t>
+          <t>FV26-DI-UNI</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5057,34 +5037,38 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>15</v>
+      </c>
+      <c r="J34" t="n">
+        <v>15</v>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>observed</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
     </row>
@@ -5096,17 +5080,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>WDI-04</t>
+          <t>WDI-03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>village</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FV26-DI-GUN</t>
+          <t>WDI-03</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -5126,19 +5110,19 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>pump_yield</t>
+          <t>village_change</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>5-7 strokes -&gt; 2 L</t>
+          <t>No impact from DI seen</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>observed</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -5148,11 +5132,19 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Strokes per litre; not convertible to L/min without timing.</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+          <t>Naula is the only source when JJM does not supply | Geologist found no link between the DI handpump and the naula.</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5167,12 +5159,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FV26-DI-GUN</t>
+          <t>RDI-SPR-0004</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5192,14 +5184,14 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J36" t="n">
         <v>9</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7–9</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -5214,7 +5206,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
+          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated. The report prints Chopdiyal Gaon as the village; Malani is at Gunogi (report error, confirmed by Rajat).</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
@@ -5233,12 +5225,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FV26-DI-GUN</t>
+          <t>RDI-SPR-0004</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5258,19 +5250,23 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>village_change</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="J37" t="n">
+        <v>17.09</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Handpump flow has increased</t>
+          <t>2 L in 7.58 s; 2 L in 6.5 s; 2 L in 7.07 s</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -5280,19 +5276,11 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Handpump gave less water</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>access</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
+          <t>Mean of 3 bucket-and-stopwatch readings, whole flow caught at the outlet pipe.</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5307,66 +5295,58 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FV26-DI-GUN</t>
+          <t>RDI-SPR-0004</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>after_di</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>village_change</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>lean_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>7</v>
+      </c>
+      <c r="J38" t="n">
+        <v>7</v>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Iron is still the main concern</t>
+          <t>7 L/min</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>High iron in handpump water</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>quality</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>unclear</t>
-        </is>
-      </c>
+          <t>Dry-season flow before DI.</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5376,7 +5356,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>WDI-05</t>
+          <t>WDI-04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5386,12 +5366,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>RDI-SPR-0005</t>
+          <t>RDI-SPR-0004</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5399,36 +5379,40 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
+          <t>lean_flow_lpm</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>4–6</t>
+          <t>10 L/min</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated. The report prints Gunogi as the village; Nimbujhard is at Chopriyal 2 (report error, confirmed by Rajat).</t>
+          <t>Dry-season flow after DI.</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
@@ -5442,7 +5426,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>WDI-05</t>
+          <t>WDI-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5452,7 +5436,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>RDI-SPR-0005</t>
+          <t>RDI-SPR-0004</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5472,33 +5456,33 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
+          <t>monsoon_flow_lpm</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>24.04</v>
+        <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>24.04</v>
+        <v>17</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2 L in 4.9 s; 2 L in 5.3 s; 2 L in 4.8 s</t>
+          <t>17 L/min</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Mean of 3 bucket-and-stopwatch readings, whole flow caught at the outlet pipe.</t>
+          <t>Monsoon flow after DI.</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
@@ -5512,7 +5496,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WDI-05</t>
+          <t>WDI-04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5522,7 +5506,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>RDI-SPR-0005</t>
+          <t>RDI-SPR-0004</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5542,18 +5526,14 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>7</v>
-      </c>
-      <c r="J41" t="n">
-        <v>9</v>
-      </c>
+          <t>reported_change</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>7-9 L/min</t>
+          <t>increase</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -5568,7 +5548,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Typical flow people gave for this season now.</t>
+          <t xml:space="preserve">Flow compared with 10-20 years ago: More. </t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
@@ -5582,63 +5562,55 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>WDI-05</t>
+          <t>WDI-04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>RDI-SPR-0005</t>
+          <t>FV26-DI-GUN</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>after_di</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>monsoon_flow_lpm</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>20</v>
-      </c>
-      <c r="J42" t="n">
-        <v>25</v>
-      </c>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>20-25 L/min</t>
+          <t>defunct</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Typical flow people gave for this season now.</t>
+          <t>People said it gave less water and had high iron before DI</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
@@ -5652,17 +5624,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>WDI-05</t>
+          <t>WDI-04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>RDI-SPR-0005</t>
+          <t>FV26-DI-GUN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5682,31 +5654,27 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>reported_change</t>
+          <t>pump_status</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>increase</t>
+          <t>working</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Flow compared with 10-20 years ago: More. Used by nearby houses; discharge had improved</t>
-        </is>
-      </c>
+          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
     </row>
@@ -5718,7 +5686,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>WDI-05</t>
+          <t>WDI-04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5728,45 +5696,49 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FV26-DI-CHP2</t>
+          <t>FV26-DI-GUN</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>before_di_recall</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>before_di</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>pump_status</t>
+          <t>pump_yield</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>defunct</t>
+          <t>5-7 strokes -&gt; 2 L</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>observed</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026 (recalled on 2026-10-19)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Handpump was defunct, with red/brown high-iron water, before DI</t>
+          <t>Strokes per litre; not convertible to L/min without timing.</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
@@ -5780,7 +5752,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>WDI-05</t>
+          <t>WDI-04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5790,12 +5762,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FV26-DI-CHP2</t>
+          <t>FV26-DI-GUN</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5803,36 +5775,36 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>9</v>
+      </c>
+      <c r="J45" t="n">
+        <v>9</v>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>observed</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Pump condition not recorded; people said it has water in the dry season now</t>
+          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
@@ -5846,7 +5818,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>WDI-05</t>
+          <t>WDI-04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5856,7 +5828,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FV26-DI-CHP2</t>
+          <t>FV26-DI-GUN</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5876,14 +5848,14 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>pump_status</t>
+          <t>village_change</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>Handpump flow has increased</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5898,11 +5870,19 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>People said the handpump has water in the dry season now</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+          <t>Handpump gave less water</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5912,7 +5892,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>WDI-05</t>
+          <t>WDI-04</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5922,12 +5902,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FV26-DI-CHP2</t>
+          <t>FV26-DI-GUN</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5935,40 +5915,48 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>4</v>
-      </c>
-      <c r="J47" t="n">
-        <v>4</v>
-      </c>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Iron is still the main concern</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+          <t>High iron in handpump water</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5983,17 +5971,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FV26-DI-CHP2</t>
+          <t>RDI-SPR-0005</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6001,48 +5989,40 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>village_change</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>4</v>
+      </c>
+      <c r="J48" t="n">
+        <v>6</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Handpump has water in the dry season</t>
+          <t>4–6</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Handpump water very bad (red/brown), handpump defunct | DI line is now disconnected (house construction).</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>quality</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
+          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated. The report prints Gunogi as the village; Nimbujhard is at Chopriyal 2 (report error, confirmed by Rajat).</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6082,19 +6062,23 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>village_change</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="J49" t="n">
+        <v>24.04</v>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Discharge has improved</t>
+          <t>2 L in 4.9 s; 2 L in 5.3 s; 2 L in 4.8 s</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -6104,19 +6088,11 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Lower spring flow</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>access</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
+          <t>Mean of 3 bucket-and-stopwatch readings, whole flow caught at the outlet pipe.</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6126,7 +6102,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WDI-06</t>
+          <t>WDI-05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6136,49 +6112,49 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>RDI-SPR-0006</t>
+          <t>RDI-SPR-0005</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>after_di</t>
+          <t>before_di</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
+          <t>lean_flow_lpm</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1.5–2</t>
+          <t>6 L/min</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated.</t>
+          <t>Dry-season flow before DI.</t>
         </is>
       </c>
       <c r="O50" t="inlineStr"/>
@@ -6192,7 +6168,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WDI-06</t>
+          <t>WDI-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6202,7 +6178,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>RDI-SPR-0006</t>
+          <t>RDI-SPR-0005</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6217,38 +6193,38 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
+          <t>lean_flow_lpm</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1-2 L/min (inflow captured inside tank)</t>
+          <t>9 L/min</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Estimated by looking at the source, not timed.</t>
+          <t>Dry-season flow after DI.</t>
         </is>
       </c>
       <c r="O51" t="inlineStr"/>
@@ -6262,7 +6238,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WDI-06</t>
+          <t>WDI-05</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6272,7 +6248,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>RDI-SPR-0006</t>
+          <t>RDI-SPR-0005</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6287,34 +6263,38 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>reported_change</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>monsoon_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>24</v>
+      </c>
+      <c r="J52" t="n">
+        <v>24</v>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>24 L/min</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Flow compared with 10-20 years ago: Dries at times. Main source; when it dries people fetch from Balench; flow has stayed similar (dries in lean months)</t>
+          <t>Monsoon flow after DI.</t>
         </is>
       </c>
       <c r="O52" t="inlineStr"/>
@@ -6328,7 +6308,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WDI-06</t>
+          <t>WDI-05</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6338,34 +6318,34 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RDI-SPR-0006</t>
+          <t>RDI-SPR-0005</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>before_di_recall</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>before_di</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
+          <t>reported_change</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>0 L/min</t>
+          <t>increase</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -6375,12 +6355,12 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026 (recalled on 2026-10-18)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>People said the flow has stayed similar: it still dries every summer.</t>
+          <t>Flow compared with 10-20 years ago: More. Used by nearby houses; discharge had improved</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
@@ -6394,63 +6374,55 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WDI-06</t>
+          <t>WDI-05</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>RDI-SPR-0006</t>
+          <t>FV26-DI-CHP2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>after_di</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0 L/min</t>
+          <t>defunct</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>People said the flow has stayed similar: it still dries every summer.</t>
+          <t>Defunct, with red/brown high-iron water, before DI</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
@@ -6464,7 +6436,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WDI-06</t>
+          <t>WDI-05</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6474,7 +6446,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>FV26-DI-ARK2</t>
+          <t>FV26-DI-CHP2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6489,7 +6461,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6501,22 +6473,22 @@
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>working</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>observed</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Pump condition not recorded</t>
+          <t>Pump box not ticked on the form; people said it has water in the dry season</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
@@ -6530,7 +6502,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WDI-06</t>
+          <t>WDI-05</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6540,7 +6512,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>FV26-DI-ARK2</t>
+          <t>FV26-DI-CHP2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6560,14 +6532,14 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6596,17 +6568,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WDI-06</t>
+          <t>WDI-05</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>village</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>WDI-06</t>
+          <t>FV26-DI-CHP2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6621,7 +6593,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6633,7 +6605,7 @@
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Still dries every summer</t>
+          <t>Handpump has water in the dry season</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6648,17 +6620,17 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Dries in lean months; people fetch water from Balench | Arakot 2 DI may feed this spring; no change reported.</t>
+          <t>Handpump water very bad (red/brown), handpump defunct | DI line is now disconnected (house construction).</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>access</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>better</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6642,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WDI-07</t>
+          <t>WDI-05</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6680,12 +6652,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>RDI-SPR-0007</t>
+          <t>RDI-SPR-0005</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6693,40 +6665,48 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
-        <v>16</v>
-      </c>
-      <c r="J58" t="n">
-        <v>16</v>
-      </c>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>~16</t>
+          <t>Discharge has improved</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated.</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
+          <t>Lower spring flow</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6736,7 +6716,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WDI-07</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6746,12 +6726,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>RDI-SPR-0007</t>
+          <t>RDI-SPR-0006</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6759,40 +6739,36 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>flow_lpm</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>21.72</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
-        <v>21.72</v>
+        <v>2</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2 L in 5.8 s; 2 L in 5.5 s; 2 L in 5.3 s</t>
+          <t>1.5–2</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Mean of 3 bucket-and-stopwatch readings, whole flow caught at the outlet pipe.</t>
+          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated.</t>
         </is>
       </c>
       <c r="O59" t="inlineStr"/>
@@ -6806,7 +6782,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WDI-07</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6816,7 +6792,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>RDI-SPR-0007</t>
+          <t>RDI-SPR-0006</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6831,28 +6807,28 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
+          <t>flow_lpm</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>10-15 L/min</t>
+          <t>1-2 L/min (inflow captured inside tank)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6862,7 +6838,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Typical flow people gave for this season now.</t>
+          <t>Estimated by looking at the source, not timed.</t>
         </is>
       </c>
       <c r="O60" t="inlineStr"/>
@@ -6876,7 +6852,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WDI-07</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6886,53 +6862,49 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>RDI-SPR-0007</t>
+          <t>RDI-SPR-0006</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>after_di</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>monsoon_flow_lpm</t>
+          <t>lean_flow_lpm</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>20-25 L/min</t>
+          <t>0 L/min</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Typical flow people gave for this season now.</t>
+          <t>Dry-season flow before DI.</t>
         </is>
       </c>
       <c r="O61" t="inlineStr"/>
@@ -6946,7 +6918,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WDI-07</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6956,7 +6928,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>RDI-SPR-0007</t>
+          <t>RDI-SPR-0006</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6971,34 +6943,38 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>reported_change</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>lean_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>increase</t>
+          <t>0 L/min</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Flow compared with 10-20 years ago: More. Nearby houses use this spring; flow has increased</t>
+          <t>Dry-season flow after DI.</t>
         </is>
       </c>
       <c r="O62" t="inlineStr"/>
@@ -7012,55 +6988,63 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WDI-07</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FV26-DI-KAN</t>
+          <t>RDI-SPR-0006</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>before_di_recall</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>before_di</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>monsoon_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J63" t="n">
+        <v>4</v>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>no_water_dry_season</t>
+          <t>4 L/min</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026 (recalled on 2026-10-19)</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Handpump has water in the dry season now (implies it did not before)</t>
+          <t>Monsoon flow after DI.</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
@@ -7074,17 +7058,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WDI-07</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>FV26-DI-KAN</t>
+          <t>RDI-SPR-0006</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7099,24 +7083,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>pump_status</t>
+          <t>reported_change</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>same</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>observed</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7124,7 +7108,11 @@
           <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Flow compared with 10-20 years ago: Dries at times. Main source; when it dries people fetch from Balench; flow has stayed similar (dries in lean months)</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
     </row>
@@ -7136,7 +7124,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WDI-07</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7146,51 +7134,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FV26-DI-KAN</t>
+          <t>FV26-DI-ARK2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>after_di</t>
+          <t>before_di</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
-        </is>
-      </c>
-      <c r="I65" t="n">
-        <v>16</v>
-      </c>
-      <c r="J65" t="n">
-        <v>16</v>
-      </c>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>defunct</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
-        </is>
-      </c>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
     </row>
@@ -7202,7 +7182,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WDI-07</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7212,7 +7192,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>FV26-DI-KAN</t>
+          <t>FV26-DI-ARK2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7227,46 +7207,38 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>village_change</t>
+          <t>pump_status</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Has water in the dry season; very good quality, travellers drink and wash</t>
+          <t>working</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Handpump had no water in the dry season</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>access</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
+          <t>Pump box not ticked on the form; Working (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7276,22 +7248,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WDI-07</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>RDI-SPR-0007</t>
+          <t>FV26-DI-ARK2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7299,48 +7271,40 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>village_change</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>3</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3</v>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Flow has increased</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Lower spring flow</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>access</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
+          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7350,40 +7314,44 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WDI-08</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>village</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>FV26-DI-KUN</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>before_di_recall</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>before_di</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>pump_status</t>
+          <t>village_change</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>defunct</t>
+          <t>Still dries every summer</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7393,16 +7361,24 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026 (recalled on 2026-10-21)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>DI was fitted on a previously defunct handpump</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
+          <t>Dries in lean months; people fetch water from Balench | Arakot 2 DI may feed this spring; no change reported.</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7412,22 +7388,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WDI-08</t>
+          <t>WDI-07</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>FV26-DI-KUN</t>
+          <t>RDI-SPR-0007</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7435,36 +7411,36 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>16</v>
+      </c>
+      <c r="J69" t="n">
+        <v>16</v>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>~16</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>observed</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Water tapped directly from the handpump</t>
+          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated.</t>
         </is>
       </c>
       <c r="O69" t="inlineStr"/>
@@ -7478,71 +7454,999 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>WDI-07</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>RDI-SPR-0007</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>field_visit_2026_10</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="J70" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2 L in 5.8 s; 2 L in 5.5 s; 2 L in 5.3 s</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Mean of 3 bucket-and-stopwatch readings, whole flow caught at the outlet pipe.</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>OBS-070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>WDI-07</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>RDI-SPR-0007</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>before_di_agreed</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>lean_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>12</v>
+      </c>
+      <c r="J71" t="n">
+        <v>12</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>12 L/min</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>agreed</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Dry-season flow before DI.</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>OBS-071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>WDI-07</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>RDI-SPR-0007</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>field_visit_2026_10</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>lean_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>15</v>
+      </c>
+      <c r="J72" t="n">
+        <v>15</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>15 L/min</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>agreed</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Dry-season flow after DI.</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>OBS-072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>WDI-07</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>RDI-SPR-0007</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>field_visit_2026_10</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>monsoon_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>22</v>
+      </c>
+      <c r="J73" t="n">
+        <v>22</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>22 L/min</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>agreed</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Monsoon flow after DI.</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>OBS-073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>WDI-07</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>RDI-SPR-0007</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>field_visit_2026_10</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>reported_change</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>increase</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Flow compared with 10-20 years ago: More. Nearby houses use this spring; flow has increased</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>OBS-074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>WDI-07</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>handpump</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>FV26-DI-KAN</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>before_di_agreed</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>defunct</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>agreed</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>People said it has water in the dry season now</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>OBS-075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>WDI-07</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>handpump</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>FV26-DI-KAN</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>field_visit_2026_10</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>working</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>agreed</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>OBS-076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>WDI-07</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>handpump</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>FV26-DI-KAN</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>watsan_report</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>16</v>
+      </c>
+      <c r="J77" t="n">
+        <v>16</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>OBS-077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>WDI-07</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>handpump</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>FV26-DI-KAN</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>field_visit_2026_10</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Has water in the dry season; very good quality, travellers drink and wash</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Handpump had no water in the dry season</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>OBS-078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>WDI-07</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>RDI-SPR-0007</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>field_visit_2026_10</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Flow has increased</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Lower spring flow</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>OBS-079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>WDI-08</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>handpump</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>FV26-DI-KUN</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>before_di_agreed</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>defunct</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>agreed</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>DI was fitted on a previously defunct handpump</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>OBS-080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>WDI-08</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>handpump</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>FV26-DI-KUN</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
         <is>
           <t>field_visit_2026_10</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>after_di</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>working</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>agreed</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Water tapped directly from the handpump</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>OBS-081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>WDI-08</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>handpump</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>FV26-DI-KUN</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>field_visit_2026_10</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
         <is>
           <t>village_change</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
         <is>
           <t>Handpump working; water tapped directly</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>Handpump defunct</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>access</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>better</t>
         </is>
       </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>OBS-082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>WDI-09</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>handpump</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>SRC028-DI-DUN</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>before_di_agreed</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>defunct</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>agreed</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>OBS-083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>WDI-09</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>handpump</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>SRC028-DI-DUN</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>after_di_agreed</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>working</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>agreed</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Not visited; Working (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
+++ b/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -502,22 +502,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ranges</t>
+          <t>remarks</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>value_low and value_high keep the range as given. Nothing is replaced by a midpoint here.</t>
+          <t>Handpump table: one short line on water quality, breakages and the DI line, from the field forms.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>impact_beyond_water</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sites table: a short account of what people told us in the community interaction part of the field form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ranges</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>value_low and value_high keep the range as given. Nothing is replaced by a midpoint here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Not included</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Photos, scanned forms and people's names.</t>
         </is>
@@ -534,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,55 +629,80 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>rain_chirps_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rain_monsoon_share_pct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>rain_dry_season_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>snow_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>households</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>people</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>handpump_ids</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>di_link_status</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>report_catchment_ha</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>visit_date</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>water_before</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>community_notes</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>impact_beyond_water</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>top_concerns</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>other_works</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -711,55 +760,76 @@
           <t>1700.8</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>1650.6</t>
-        </is>
+      <c r="L2" t="n">
+        <v>1109</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>CHIRPS 2018-2025 mean at the spring (as the planner)</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+          <t>IMD gridded rain gauges, mean of 2001-2025 (24 years; missing 2012)</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>1651</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>222.4</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>FV26-DI-ARK1;FV26-DI-ARK2</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Reported by WATSAN (both Arakot 1 and 2); not verified</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>33.53</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Lean flow 1-2 before, 2-3 L/min now (guide); handpump was defunct before DI, now has water in dry season; water decent, slight iron</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>A handpump that had stood defunct now gives water through the dry season, and the spring's dry-season flow has doubled. The water is decent to drink. Fixing the broken rooftop pipe at Arakot 1 will keep this going.</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Roof pipe broken at Arakot 1</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Check dams</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Comparison spring without DI named on form: Paniyar Dhar.</t>
         </is>
@@ -821,67 +891,88 @@
           <t>1803.4</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>1650.6</t>
-        </is>
+      <c r="L3" t="n">
+        <v>1332</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>CHIRPS 2018-2025 mean at the spring (as the planner)</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+          <t>IMD gridded rain gauges, mean of 2001-2025 (24 years; missing 2012)</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1651</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>222.4</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>FV26-DI-CHP1</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Reported (Chopriyal 1); not verified</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>43.55</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Discharge reportedly increased in further springs downhill (Silogi village); water quality good</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Entire village depends on the solar pumping project; before: severe water crisis, 2-3 km walk downhill; now water available, vegetation and farming</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Families once walked 2-3 km downhill for water. Today all 28 households (about 200 people) have water in the village, and it now supports vegetation and farming. People also report more water in springs further downhill at Silogi. The Himmotthan solar pumping scheme works alongside DI here.</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>No concern</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Check dams and DI</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -939,63 +1030,84 @@
           <t>2365.1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1920.0</t>
-        </is>
+      <c r="L4" t="n">
+        <v>1332</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>CHIRPS 2018-2025 mean at the spring (as the planner)</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+          <t>IMD gridded rain gauges, mean of 2001-2025 (24 years; missing 2012)</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1920</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>228.2</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>FV26-DI-UNI</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Not established: geologist could not find a connection (DTR claims one)</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>53.67</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Only source when JJM is not supplying; no impact from DI</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>The naula is the only fallback for 2 households (about 10 people) when the JJM tap fails. People saw no change from DI, and the school handpump is now broken.</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
         <is>
           <t>DI should be left out (it is not recharging the naula)</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Summary table gives 1-2 L/min; form 2-3 L/min (form used). Naula discharge method seen: mark level on a stick, remove 1 L, time the refill.</t>
         </is>
@@ -1053,55 +1165,76 @@
           <t>1753.4</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1650.6</t>
-        </is>
+      <c r="L5" t="n">
+        <v>1446</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>CHIRPS 2018-2025 mean at the spring (as the planner)</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+          <t>IMD gridded rain gauges, mean of 2001-2025 (24 years; missing 2012)</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1651</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>73.7</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>222.4</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>FV26-DI-GUN</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Reported (Gunogi); not verified</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>18.12</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Handpump flow increased; handpump water had high iron</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>The Gunogi handpump gives more water than before DI, and the spring's dry-season flow has risen. Iron in the handpump water is still people's main worry, so a water test is the next step.</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Iron content</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Trenches and check dam</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>DTR places this spring at Chopdiyal Gaon; field and photo GPS place it at Gunogi.</t>
         </is>
@@ -1159,63 +1292,84 @@
           <t>2010.1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>1650.6</t>
-        </is>
+      <c r="L6" t="n">
+        <v>1332</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CHIRPS 2018-2025 mean at the spring (as the planner)</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+          <t>IMD gridded rain gauges, mean of 2001-2025 (24 years; missing 2012)</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1651</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>222.4</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
         <is>
           <t>FV26-DI-CHP2</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Reported (Chopriyal 2); DI currently disconnected</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>20.67</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Handpump has water in dry season; handpump water was very bad (red/brown) before DI</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Used by nearby houses; discharge had improved</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Before DI the handpump water was red-brown and people could not use it. Now it has water through the dry season, and the spring that about 20 nearby households use flows better. Reconnecting the DI line, cut during house construction, is the priority.</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Disconnected DI</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Check dams; oak (banj) and burans trees</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>DTR places this spring at Gunogi; field and photo GPS place it at Chopriyal 2.</t>
         </is>
@@ -1273,55 +1427,76 @@
           <t>1697.9</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1650.6</t>
-        </is>
+      <c r="L7" t="n">
+        <v>1109</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>CHIRPS 2018-2025 mean at the spring (as the planner)</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+          <t>IMD gridded rain gauges, mean of 2001-2025 (24 years; missing 2012)</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1651</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>222.4</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>FV26-DI-ARK2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Arakot 2 may feed Paniyar Dhar as well as Balench (Rajat, 2026-10-24); not verified</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>45.03</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr">
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Main source; when it dries people fetch from Balench; flow has stayed similar (dries in lean months)</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>The spring still dries in the lean months, and people walk to Balench for water then. It now flows in the monsoon.</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Dries in lean months; no DI connection</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Check dam</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Summary table lists 'Paniyar dhara (1 and 2)', 2-3 L/min, zero in summer; form today 1-2 L/min (form used).</t>
         </is>
@@ -1383,59 +1558,80 @@
           <t>2256.0</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>1897.9</t>
-        </is>
+      <c r="L8" t="n">
+        <v>1332</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>CHIRPS 2018-2025 mean at the spring (as the planner)</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+          <t>IMD gridded rain gauges, mean of 2001-2025 (24 years; missing 2012)</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1898</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>71.2</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>238.0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>FV26-DI-KAN</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Reported (Kanatal); not verified</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>19.35</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Handpump has water in dry season; very good quality, travellers drink and wash</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Nearby houses use this spring; flow has increased</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>The Kanatal handpump now has water in the dry season, and it is very good quality: travellers stop to drink and wash. Nearby houses say the spring flow has gone up. The roadside DI site needs regular cleaning.</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
         <is>
           <t>DI site is very dirty (roadside)</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>DI site; check dams and trenches</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1485,39 +1681,60 @@
           <t>1491.4</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2651.2</t>
-        </is>
+      <c r="L9" t="n">
+        <v>1446</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>CHIRPS 2018-2025 mean at the spring (as the planner)</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+          <t>IMD gridded rain gauges, mean of 2001-2025 (24 years; missing 2012)</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2651</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>73.7</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>200.9</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>FV26-DI-KUN</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>SRHU Badera hydrogeology report (SRC-027): handpump upslope of Badeda Spring in the same shallow fractured Krol Group aquifer; report handpump point is about 30 m from the field GPS</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>40.51</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>A handpump that was defunct works again, and people tap water from it directly.</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1567,39 +1784,56 @@
           <t>1479.6</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2105.0</t>
-        </is>
+      <c r="L10" t="n">
+        <v>1332</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>CHIRPS 2018-2025 mean at the spring (as the planner)</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+          <t>IMD gridded rain gauges, mean of 2001-2025 (24 years; missing 2012)</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>2105</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>71.2</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>232.3</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>SRC028-DI-DUN</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Reported by the SRHU report (SRC-028); not visited</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>91.07</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1612,7 +1846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1741,6 +1975,21 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>remarks</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>location_class</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>location_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1858,6 +2107,21 @@
           <t>Delivery test 6-7 strokes for 1-2 L; Roof pipe broken; Exposed plastic roof pipe along the road; Depth on the form 100 m, reduced by 30 m (Rajat 2026-10-23: form depths were recorded about 30 m high)</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Has water in the dry season; water decent, slight iron. Rooftop pipe broken, so the DI line is disconnected.</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>in_catchment</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1967,6 +2231,21 @@
           <t>Pump box not ticked on the form; Working (Rajat, 2026-10-24); Tested during visit; Depth on the form 100 m, reduced by 30 m (Rajat 2026-10-23: form depths were recorded about 30 m high)</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>DI tested on the visit. Linked to both Balench and Paniyar Dhar (not verified).</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>in_catchment</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2080,6 +2359,21 @@
           <t>Working; Depth on the form 90 m, reduced by 30 m (Rajat 2026-10-23: form depths were recorded about 30 m high)</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>DI line, gutter and filter in good order.</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>in_catchment</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2166,7 +2460,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>broken</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2192,7 +2486,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Field form recorded it broken (possible vehicle damage); Working (Rajat, 2026-10-24); Pump broken; Installed last year for the school; possible vehicle damage (not confirmed); Depth on the form 90 m, reduced by 30 m (Rajat 2026-10-23: form depths were recorded about 30 m high)</t>
+          <t>Handpump broken, possible vehicle damage (field form; confirmed by Rajat, 2026-10-24); Pump broken; Installed last year for the school; possible vehicle damage (not confirmed); Depth on the form 90 m, reduced by 30 m (Rajat 2026-10-23: form depths were recorded about 30 m high)</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Handpump broken (possible vehicle damage). First flush not working, filter blocked.</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Geologist found no connection between this handpump and the naula.</t>
         </is>
       </c>
     </row>
@@ -2310,6 +2619,21 @@
       <c r="Y6" t="inlineStr">
         <is>
           <t>Working; Safety flag: water quality (iron in handpump water); Depth on the form 100 (300 ft) m, reduced by 30 m (Rajat 2026-10-23: form depths were recorded about 30 m high)</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Gives more water than before DI. Iron in the water is still a concern.</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>in_catchment</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
         </is>
       </c>
     </row>
@@ -2413,6 +2737,21 @@
           <t>Pump box not ticked on the form; people said it has water in the dry season; Disconnected (house construction); Handpump was defunct with high-iron water before DI; reported improvement after DI (no lab results); Depth on the form 110 m, set to 40 m by Rajat (2026-10-23)</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Water quality improved: it was red/brown with high iron before DI (no lab test). DI line disconnected during house construction; filter blocked.</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>in_catchment</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2518,6 +2857,21 @@
           <t>Pump box not ticked on the form; Working (Rajat, 2026-10-24); Tested during visit; Depth on the form 100 m, reduced by 30 m (Rajat 2026-10-23: form depths were recorded about 30 m high)</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>DI tested on the visit. Linked to both Balench and Paniyar Dhar (not verified).</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>in_catchment</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2625,6 +2979,21 @@
       <c r="Y9" t="inlineStr">
         <is>
           <t>Working; Roadside, heavy litter; safety flag: clogging/dirty inflow; Depth on the form 100 m, reduced by 30 m (Rajat 2026-10-23: form depths were recorded about 30 m high)</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Water in the dry season, very good quality; travellers drink and wash here. Roadside DI site is dirty.</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>in_catchment</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
         </is>
       </c>
     </row>
@@ -2720,6 +3089,21 @@
       <c r="Y10" t="inlineStr">
         <is>
           <t>Water tapped directly from the handpump; Working (recent DI on a previously defunct handpump); Exposed plastic roof pipes; animal and monkey damage risk</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Working again; people tap water directly. Exposed roof pipes at risk from animals and monkeys.</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>in_catchment</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
         </is>
       </c>
     </row>
@@ -2785,6 +3169,13 @@
           <t>Not visited; Working (Rajat, 2026-10-24)</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Not visited; from the SRHU report.</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2797,7 +3188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P84"/>
+  <dimension ref="A1:P91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3756,7 +4147,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WDI-02</t>
+          <t>WDI-01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3766,12 +4157,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>RDI-SPR-0002</t>
+          <t>RDI-SPR-0001</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3779,40 +4170,48 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>12</v>
-      </c>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8–12</t>
+          <t>Dry-season flow about 2-3 L/min</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated.</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+          <t>Dry-season flow about 1-2 L/min</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3822,17 +4221,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WDI-02</t>
+          <t>WDI-01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>RDI-SPR-0002</t>
+          <t>FV26-DI-ARK1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3852,19 +4251,19 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
+          <t>village_change</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Could not measure, but perennial</t>
+          <t>Rooftop pipe broken, so no roof water reaches the handpump</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>not_measured</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -3872,9 +4271,21 @@
           <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>DI line carried roof water to Arakot 1</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>upkeep</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>worse</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3899,44 +4310,44 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>before_di_agreed</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>before_di</t>
+          <t>after_di</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
+          <t>flow_lpm</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>8</v>
       </c>
       <c r="J17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8 L/min</t>
+          <t>8–12</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Dry-season flow before DI.</t>
+          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -3980,35 +4391,27 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>12</v>
-      </c>
-      <c r="J18" t="n">
-        <v>12</v>
-      </c>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>12 L/min</t>
+          <t>Could not measure, but perennial</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>not_measured</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Dry-season flow after DI.</t>
-        </is>
-      </c>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
     </row>
@@ -4035,33 +4438,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>after_di</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>monsoon_flow_lpm</t>
+          <t>lean_flow_lpm</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>20 L/min</t>
+          <t>8 L/min</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -4076,7 +4475,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Monsoon flow after DI.</t>
+          <t>Dry-season flow before DI.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -4120,29 +4519,33 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>reported_change</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>lean_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>12</v>
+      </c>
+      <c r="J20" t="n">
+        <v>12</v>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>increase</t>
+          <t>12 L/min</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Flow compared with 10-20 years ago: More. Entire village depends on the solar pumping project; before: severe water crisis, 2-3 km walk downhill; now water available, vegetation and farming</t>
+          <t>Dry-season flow after DI.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
@@ -4161,35 +4564,43 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FV26-DI-CHP1</t>
+          <t>RDI-SPR-0002</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>before_di_agreed</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>before_di</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>monsoon_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>20</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20</v>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>defunct</t>
+          <t>20 L/min</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -4199,10 +4610,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Monsoon flow after DI.</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
     </row>
@@ -4219,12 +4634,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FV26-DI-CHP1</t>
+          <t>RDI-SPR-0002</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4244,27 +4659,31 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>pump_status</t>
+          <t>reported_change</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>increase</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Flow compared with 10-20 years ago: More. Entire village depends on the solar pumping project; before: severe water crisis, 2-3 km walk downhill; now water available, vegetation and farming</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
     </row>
@@ -4291,46 +4710,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>after_di</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>pump_yield</t>
+          <t>pump_status</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>7-8 strokes -&gt; 1-2 L</t>
+          <t>defunct</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>observed</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Strokes per litre; not convertible to L/min without timing.</t>
-        </is>
-      </c>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
     </row>
@@ -4357,7 +4768,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4365,38 +4776,34 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>12</v>
-      </c>
-      <c r="J24" t="n">
-        <v>12</v>
-      </c>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>working</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
-        </is>
-      </c>
+          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
     </row>
@@ -4413,12 +4820,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>village</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>WDI-02</t>
+          <t>FV26-DI-CHP1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4438,19 +4845,19 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>village_change</t>
+          <t>pump_yield</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Water available in the village; vegetation and farming</t>
+          <t>7-8 strokes -&gt; 1-2 L</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>observed</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -4460,19 +4867,11 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Severe water crisis; people walked 2-3 km downhill for water | Himmotthan solar pumping from the spring is a separate scheme and explains much of this.</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>access</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
+          <t>Strokes per litre; not convertible to L/min without timing.</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4482,17 +4881,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WDI-03</t>
+          <t>WDI-02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>RDI-SPR-0003</t>
+          <t>FV26-DI-CHP1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4512,14 +4911,14 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J26" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>8–15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -4534,7 +4933,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated.</t>
+          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
@@ -4548,17 +4947,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WDI-03</t>
+          <t>WDI-02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>village</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>RDI-SPR-0003</t>
+          <t>WDI-02</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4573,28 +4972,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3</v>
-      </c>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2-3 L/min (estimate from looking at the source)</t>
+          <t>Water available in the village for all 28 households (about 200 people)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -4604,11 +4999,19 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Estimated by looking at the source, not timed.</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+          <t>Severe water crisis; people walked 2-3 km downhill for water | Himmotthan solar pumping from the spring is a separate scheme and explains much of this.</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4618,63 +5021,71 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WDI-03</t>
+          <t>WDI-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>village</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>RDI-SPR-0003</t>
+          <t>WDI-02</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>before_di_agreed</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>before_di</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3</v>
-      </c>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>3 L/min</t>
+          <t>Vegetation and farming have come back with the water</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Dry-season flow before DI.</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+          <t>Little water for plants or fields</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>vegetation</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4684,7 +5095,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WDI-03</t>
+          <t>WDI-02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4694,7 +5105,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>RDI-SPR-0003</t>
+          <t>RDI-SPR-0002</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4709,42 +5120,46 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>3</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3</v>
-      </c>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3 L/min</t>
+          <t>People report more water in the downhill springs; water quality good</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Dry-season flow after DI.</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+          <t>Lower flow in springs downhill at Silogi</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4769,7 +5184,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4777,40 +5192,36 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>monsoon_flow_lpm</t>
+          <t>flow_lpm</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>10 L/min</t>
+          <t>8–15</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Monsoon flow after DI.</t>
+          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated.</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
@@ -4854,19 +5265,23 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>reported_change</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>2-3 L/min (estimate from looking at the source)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -4876,7 +5291,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Flow compared with 10-20 years ago: Same. Only source when JJM is not supplying; no impact from DI</t>
+          <t>Estimated by looking at the source, not timed.</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
@@ -4895,12 +5310,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FV26-DI-UNI</t>
+          <t>RDI-SPR-0003</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4916,14 +5331,18 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>lean_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>defunct</t>
+          <t>3 L/min</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -4933,10 +5352,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Dry-season flow before DI.</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
     </row>
@@ -4953,12 +5376,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FV26-DI-UNI</t>
+          <t>RDI-SPR-0003</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4978,14 +5401,18 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>lean_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>3 L/min</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -4995,12 +5422,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Field form recorded it broken (possible vehicle damage); Working (Rajat, 2026-10-24)</t>
+          <t>Dry-season flow after DI.</t>
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
@@ -5019,17 +5446,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FV26-DI-UNI</t>
+          <t>RDI-SPR-0003</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5037,36 +5464,40 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
+          <t>monsoon_flow_lpm</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10 L/min</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
+          <t>Monsoon flow after DI.</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
@@ -5085,12 +5516,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>village</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>WDI-03</t>
+          <t>RDI-SPR-0003</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -5110,14 +5541,14 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>village_change</t>
+          <t>reported_change</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>No impact from DI seen</t>
+          <t>same</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -5132,19 +5563,11 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Naula is the only source when JJM does not supply | Geologist found no link between the DI handpump and the naula.</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>access</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
+          <t>Flow compared with 10-20 years ago: Same. Only source when JJM is not supplying; no impact from DI</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5154,61 +5577,53 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WDI-04</t>
+          <t>WDI-03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>RDI-SPR-0004</t>
+          <t>FV26-DI-UNI</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>after_di</t>
+          <t>before_di</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>7</v>
-      </c>
-      <c r="J36" t="n">
-        <v>9</v>
-      </c>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>7–9</t>
+          <t>defunct</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated. The report prints Chopdiyal Gaon as the village; Malani is at Gunogi (report error, confirmed by Rajat).</t>
-        </is>
-      </c>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
     </row>
@@ -5220,17 +5635,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WDI-04</t>
+          <t>WDI-03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>RDI-SPR-0004</t>
+          <t>FV26-DI-UNI</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5250,33 +5665,29 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>17.09</v>
-      </c>
-      <c r="J37" t="n">
-        <v>17.09</v>
-      </c>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2 L in 7.58 s; 2 L in 6.5 s; 2 L in 7.07 s</t>
+          <t>broken</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Mean of 3 bucket-and-stopwatch readings, whole flow caught at the outlet pipe.</t>
+          <t>Handpump broken, possible vehicle damage (field form; confirmed by Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
@@ -5290,59 +5701,59 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>WDI-04</t>
+          <t>WDI-03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>RDI-SPR-0004</t>
+          <t>FV26-DI-UNI</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>before_di_agreed</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>before_di</t>
+          <t>after_di</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
+          <t>flow_lpm</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J38" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>7 L/min</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Dry-season flow before DI.</t>
+          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
@@ -5356,17 +5767,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>WDI-04</t>
+          <t>WDI-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>village</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>RDI-SPR-0004</t>
+          <t>WDI-03</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5386,37 +5797,41 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>10</v>
-      </c>
-      <c r="J39" t="n">
-        <v>10</v>
-      </c>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>10 L/min</t>
+          <t>No impact from DI seen</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Dry-season flow after DI.</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+          <t>Naula is the only source when JJM does not supply | Geologist found no link between the DI handpump and the naula.</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5426,17 +5841,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>WDI-04</t>
+          <t>WDI-03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>RDI-SPR-0004</t>
+          <t>FV26-DI-UNI</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5456,37 +5871,41 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>monsoon_flow_lpm</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>17</v>
-      </c>
-      <c r="J40" t="n">
-        <v>17</v>
-      </c>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>17 L/min</t>
+          <t>Handpump broken (possible vehicle damage); first flush not working</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Monsoon flow after DI.</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+          <t>School handpump fitted with DI in 2025</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>upkeep</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>worse</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5511,7 +5930,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5519,36 +5938,36 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>reported_change</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>7</v>
+      </c>
+      <c r="J41" t="n">
+        <v>9</v>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>increase</t>
+          <t>7–9</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flow compared with 10-20 years ago: More. </t>
+          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated. The report prints Chopdiyal Gaon as the village; Malani is at Gunogi (report error, confirmed by Rajat).</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
@@ -5567,50 +5986,58 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FV26-DI-GUN</t>
+          <t>RDI-SPR-0004</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>before_di_agreed</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>before_di</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="J42" t="n">
+        <v>17.09</v>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>defunct</t>
+          <t>2 L in 7.58 s; 2 L in 6.5 s; 2 L in 7.07 s</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>People said it gave less water and had high iron before DI</t>
+          <t>Mean of 3 bucket-and-stopwatch readings, whole flow caught at the outlet pipe.</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
@@ -5629,39 +6056,39 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FV26-DI-GUN</t>
+          <t>RDI-SPR-0004</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>after_di</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>lean_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>7</v>
+      </c>
+      <c r="J43" t="n">
+        <v>7</v>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>7 L/min</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -5671,10 +6098,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Dry-season flow before DI.</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
     </row>
@@ -5691,12 +6122,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FV26-DI-GUN</t>
+          <t>RDI-SPR-0004</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5716,29 +6147,33 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>pump_yield</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>lean_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>10</v>
+      </c>
+      <c r="J44" t="n">
+        <v>10</v>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>5-7 strokes -&gt; 2 L</t>
+          <t>10 L/min</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>observed</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Strokes per litre; not convertible to L/min without timing.</t>
+          <t>Dry-season flow after DI.</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
@@ -5757,17 +6192,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FV26-DI-GUN</t>
+          <t>RDI-SPR-0004</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5775,36 +6210,40 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
+          <t>monsoon_flow_lpm</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17 L/min</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
+          <t>Monsoon flow after DI.</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
@@ -5823,12 +6262,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FV26-DI-GUN</t>
+          <t>RDI-SPR-0004</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5848,14 +6287,14 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>village_change</t>
+          <t>reported_change</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Handpump flow has increased</t>
+          <t>increase</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5870,19 +6309,11 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Handpump gave less water</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>access</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Flow compared with 10-20 years ago: More. </t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5907,56 +6338,44 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>after_di</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>village_change</t>
+          <t>pump_status</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Iron is still the main concern</t>
+          <t>defunct</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>High iron in handpump water</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>quality</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>unclear</t>
-        </is>
-      </c>
+          <t>People said it gave less water and had high iron before DI</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5966,22 +6385,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WDI-05</t>
+          <t>WDI-04</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>RDI-SPR-0005</t>
+          <t>FV26-DI-GUN</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5989,38 +6408,34 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>4</v>
-      </c>
-      <c r="J48" t="n">
-        <v>6</v>
-      </c>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>4–6</t>
+          <t>working</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated. The report prints Gunogi as the village; Nimbujhard is at Chopriyal 2 (report error, confirmed by Rajat).</t>
-        </is>
-      </c>
+          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
     </row>
@@ -6032,17 +6447,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WDI-05</t>
+          <t>WDI-04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>RDI-SPR-0005</t>
+          <t>FV26-DI-GUN</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6062,23 +6477,19 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>24.04</v>
-      </c>
-      <c r="J49" t="n">
-        <v>24.04</v>
-      </c>
+          <t>pump_yield</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2 L in 4.9 s; 2 L in 5.3 s; 2 L in 4.8 s</t>
+          <t>5-7 strokes -&gt; 2 L</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>observed</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -6088,7 +6499,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Mean of 3 bucket-and-stopwatch readings, whole flow caught at the outlet pipe.</t>
+          <t>Strokes per litre; not convertible to L/min without timing.</t>
         </is>
       </c>
       <c r="O49" t="inlineStr"/>
@@ -6102,59 +6513,59 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WDI-05</t>
+          <t>WDI-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>RDI-SPR-0005</t>
+          <t>FV26-DI-GUN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>before_di_agreed</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>before_di</t>
+          <t>after_di</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
+          <t>flow_lpm</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J50" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>6 L/min</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Dry-season flow before DI.</t>
+          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
         </is>
       </c>
       <c r="O50" t="inlineStr"/>
@@ -6168,17 +6579,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WDI-05</t>
+          <t>WDI-04</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>RDI-SPR-0005</t>
+          <t>FV26-DI-GUN</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6198,37 +6609,41 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>9</v>
-      </c>
-      <c r="J51" t="n">
-        <v>9</v>
-      </c>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>9 L/min</t>
+          <t>Handpump flow has increased</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Dry-season flow after DI.</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
+          <t>Handpump gave less water</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6238,17 +6653,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WDI-05</t>
+          <t>WDI-04</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>RDI-SPR-0005</t>
+          <t>FV26-DI-GUN</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6268,37 +6683,41 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>monsoon_flow_lpm</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>24</v>
-      </c>
-      <c r="J52" t="n">
-        <v>24</v>
-      </c>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>24 L/min</t>
+          <t>Iron is still the main concern</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Monsoon flow after DI.</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
+          <t>High iron in handpump water</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6323,7 +6742,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6331,36 +6750,36 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>reported_change</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>4</v>
+      </c>
+      <c r="J53" t="n">
+        <v>6</v>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>increase</t>
+          <t>4–6</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Flow compared with 10-20 years ago: More. Used by nearby houses; discharge had improved</t>
+          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated. The report prints Gunogi as the village; Nimbujhard is at Chopriyal 2 (report error, confirmed by Rajat).</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
@@ -6379,50 +6798,58 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>FV26-DI-CHP2</t>
+          <t>RDI-SPR-0005</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>before_di_agreed</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>before_di</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="J54" t="n">
+        <v>24.04</v>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>defunct</t>
+          <t>2 L in 4.9 s; 2 L in 5.3 s; 2 L in 4.8 s</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Defunct, with red/brown high-iron water, before DI</t>
+          <t>Mean of 3 bucket-and-stopwatch readings, whole flow caught at the outlet pipe.</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
@@ -6441,39 +6868,39 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>FV26-DI-CHP2</t>
+          <t>RDI-SPR-0005</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>after_di</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>lean_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>6</v>
+      </c>
+      <c r="J55" t="n">
+        <v>6</v>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>6 L/min</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -6483,12 +6910,12 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Pump box not ticked on the form; people said it has water in the dry season</t>
+          <t>Dry-season flow before DI.</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
@@ -6507,17 +6934,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>FV26-DI-CHP2</t>
+          <t>RDI-SPR-0005</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6525,36 +6952,40 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
+          <t>lean_flow_lpm</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J56" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9 L/min</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
+          <t>Dry-season flow after DI.</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
@@ -6573,12 +7004,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>FV26-DI-CHP2</t>
+          <t>RDI-SPR-0005</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6598,41 +7029,37 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>village_change</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>monsoon_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>24</v>
+      </c>
+      <c r="J57" t="n">
+        <v>24</v>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Handpump has water in the dry season</t>
+          <t>24 L/min</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Handpump water very bad (red/brown), handpump defunct | DI line is now disconnected (house construction).</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>quality</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
+          <t>Monsoon flow after DI.</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6672,14 +7099,14 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>village_change</t>
+          <t>reported_change</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Discharge has improved</t>
+          <t>increase</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6694,19 +7121,11 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Lower spring flow</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>access</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
+          <t>Flow compared with 10-20 years ago: More. Used by nearby houses; discharge had improved</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6716,59 +7135,55 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WDI-06</t>
+          <t>WDI-05</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>RDI-SPR-0006</t>
+          <t>FV26-DI-CHP2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>after_di</t>
+          <t>before_di</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J59" t="n">
-        <v>2</v>
-      </c>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>1.5–2</t>
+          <t>defunct</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated.</t>
+          <t>Defunct, with red/brown high-iron water, before DI</t>
         </is>
       </c>
       <c r="O59" t="inlineStr"/>
@@ -6782,17 +7197,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WDI-06</t>
+          <t>WDI-05</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>RDI-SPR-0006</t>
+          <t>FV26-DI-CHP2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6807,38 +7222,34 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" t="n">
-        <v>2</v>
-      </c>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>1-2 L/min (inflow captured inside tank)</t>
+          <t>working</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Estimated by looking at the source, not timed.</t>
+          <t>Pump box not ticked on the form; people said it has water in the dry season</t>
         </is>
       </c>
       <c r="O60" t="inlineStr"/>
@@ -6852,59 +7263,59 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WDI-06</t>
+          <t>WDI-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>RDI-SPR-0006</t>
+          <t>FV26-DI-CHP2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>before_di_agreed</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>before_di</t>
+          <t>after_di</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
+          <t>flow_lpm</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>0 L/min</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Dry-season flow before DI.</t>
+          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
         </is>
       </c>
       <c r="O61" t="inlineStr"/>
@@ -6918,17 +7329,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WDI-06</t>
+          <t>WDI-05</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>RDI-SPR-0006</t>
+          <t>FV26-DI-CHP2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6943,42 +7354,46 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
-        </is>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>0 L/min</t>
+          <t>Handpump has water in the dry season</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Dry-season flow after DI.</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+          <t>Handpump water very bad (red/brown), handpump defunct | No lab test yet.</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6988,7 +7403,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WDI-06</t>
+          <t>WDI-05</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6998,7 +7413,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>RDI-SPR-0006</t>
+          <t>RDI-SPR-0005</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7013,42 +7428,46 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>monsoon_flow_lpm</t>
-        </is>
-      </c>
-      <c r="I63" t="n">
-        <v>4</v>
-      </c>
-      <c r="J63" t="n">
-        <v>4</v>
-      </c>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>4 L/min</t>
+          <t>Discharge has improved for about 20 households</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Monsoon flow after DI.</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
+          <t>Lower spring flow</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7058,17 +7477,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WDI-06</t>
+          <t>WDI-05</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>RDI-SPR-0006</t>
+          <t>FV26-DI-CHP2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7083,19 +7502,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>reported_change</t>
+          <t>village_change</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>DI line disconnected during house construction</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -7110,11 +7529,19 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Flow compared with 10-20 years ago: Dries at times. Main source; when it dries people fetch from Balench; flow has stayed similar (dries in lean months)</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
+          <t>DI line connected</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>upkeep</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>worse</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7129,48 +7556,56 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FV26-DI-ARK2</t>
+          <t>RDI-SPR-0006</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>before_di_agreed</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>before_di</t>
+          <t>after_di</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J65" t="n">
+        <v>2</v>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>defunct</t>
+          <t>1.5–2</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated.</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
     </row>
@@ -7187,12 +7622,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>FV26-DI-ARK2</t>
+          <t>RDI-SPR-0006</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7212,29 +7647,33 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>2</v>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>1-2 L/min (inflow captured inside tank)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Pump box not ticked on the form; Working (Rajat, 2026-10-24)</t>
+          <t>Estimated by looking at the source, not timed.</t>
         </is>
       </c>
       <c r="O66" t="inlineStr"/>
@@ -7253,54 +7692,54 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>FV26-DI-ARK2</t>
+          <t>RDI-SPR-0006</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>after_di</t>
+          <t>before_di</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
+          <t>lean_flow_lpm</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0 L/min</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
+          <t>Dry-season flow before DI.</t>
         </is>
       </c>
       <c r="O67" t="inlineStr"/>
@@ -7319,12 +7758,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>village</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>WDI-06</t>
+          <t>RDI-SPR-0006</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7344,41 +7783,37 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>village_change</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>lean_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Still dries every summer</t>
+          <t>0 L/min</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Dries in lean months; people fetch water from Balench | Arakot 2 DI may feed this spring; no change reported.</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>access</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>same</t>
-        </is>
-      </c>
+          <t>Dry-season flow after DI.</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7388,7 +7823,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WDI-07</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7398,12 +7833,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>RDI-SPR-0007</t>
+          <t>RDI-SPR-0006</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7411,36 +7846,40 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
+          <t>monsoon_flow_lpm</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J69" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>~16</t>
+          <t>4 L/min</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated.</t>
+          <t>Monsoon flow after DI.</t>
         </is>
       </c>
       <c r="O69" t="inlineStr"/>
@@ -7454,7 +7893,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WDI-07</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7464,7 +7903,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>RDI-SPR-0007</t>
+          <t>RDI-SPR-0006</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7479,28 +7918,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
-        </is>
-      </c>
-      <c r="I70" t="n">
-        <v>21.72</v>
-      </c>
-      <c r="J70" t="n">
-        <v>21.72</v>
-      </c>
+          <t>reported_change</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2 L in 5.8 s; 2 L in 5.5 s; 2 L in 5.3 s</t>
+          <t>same</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>measured</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7510,7 +7945,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Mean of 3 bucket-and-stopwatch readings, whole flow caught at the outlet pipe.</t>
+          <t>Flow compared with 10-20 years ago: Dries at times. Main source; when it dries people fetch from Balench; flow has stayed similar (dries in lean months)</t>
         </is>
       </c>
       <c r="O70" t="inlineStr"/>
@@ -7524,17 +7959,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WDI-07</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>RDI-SPR-0007</t>
+          <t>FV26-DI-ARK2</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7550,18 +7985,14 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
-        </is>
-      </c>
-      <c r="I71" t="n">
-        <v>12</v>
-      </c>
-      <c r="J71" t="n">
-        <v>12</v>
-      </c>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>12 L/min</t>
+          <t>defunct</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7571,14 +8002,10 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>Dry-season flow before DI.</t>
-        </is>
-      </c>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
     </row>
@@ -7590,17 +8017,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WDI-07</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>RDI-SPR-0007</t>
+          <t>FV26-DI-ARK2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7615,23 +8042,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>lean_flow_lpm</t>
-        </is>
-      </c>
-      <c r="I72" t="n">
-        <v>15</v>
-      </c>
-      <c r="J72" t="n">
-        <v>15</v>
-      </c>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>15 L/min</t>
+          <t>working</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7641,12 +8064,12 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Dry-season flow after DI.</t>
+          <t>Pump box not ticked on the form; Working (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="O72" t="inlineStr"/>
@@ -7660,22 +8083,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WDI-07</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>handpump</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>RDI-SPR-0007</t>
+          <t>FV26-DI-ARK2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7683,40 +8106,36 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>monsoon_flow_lpm</t>
+          <t>flow_lpm</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="J73" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>22 L/min</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Monsoon flow after DI.</t>
+          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
         </is>
       </c>
       <c r="O73" t="inlineStr"/>
@@ -7730,17 +8149,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>WDI-07</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>village</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>RDI-SPR-0007</t>
+          <t>WDI-06</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7755,19 +8174,19 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>reported_change</t>
+          <t>village_change</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>increase</t>
+          <t>Still dries every summer</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7782,11 +8201,19 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Flow compared with 10-20 years ago: More. Nearby houses use this spring; flow has increased</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
+          <t>Dries in lean months; people fetch water from Balench | Arakot 2 DI may feed this spring; not verified.</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7801,50 +8228,54 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>FV26-DI-KAN</t>
+          <t>RDI-SPR-0007</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>before_di_agreed</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>before_di</t>
+          <t>after_di</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>16</v>
+      </c>
+      <c r="J75" t="n">
+        <v>16</v>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>defunct</t>
+          <t>~16</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>People said it has water in the dry season now</t>
+          <t>Report says DI was fitted at nearby handpumps; season of the reading is not stated.</t>
         </is>
       </c>
       <c r="O75" t="inlineStr"/>
@@ -7863,12 +8294,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>FV26-DI-KAN</t>
+          <t>RDI-SPR-0007</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7888,27 +8319,35 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="J76" t="n">
+        <v>21.72</v>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>2 L in 5.8 s; 2 L in 5.5 s; 2 L in 5.3 s</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Mean of 3 bucket-and-stopwatch readings, whole flow caught at the outlet pipe.</t>
+        </is>
+      </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
     </row>
@@ -7925,54 +8364,54 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>FV26-DI-KAN</t>
+          <t>RDI-SPR-0007</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>watsan_report</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>after_di</t>
+          <t>before_di</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>flow_lpm</t>
+          <t>lean_flow_lpm</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J77" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12 L/min</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
+          <t>Dry-season flow before DI.</t>
         </is>
       </c>
       <c r="O77" t="inlineStr"/>
@@ -7991,12 +8430,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>FV26-DI-KAN</t>
+          <t>RDI-SPR-0007</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8016,41 +8455,37 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>village_change</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+          <t>lean_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>15</v>
+      </c>
+      <c r="J78" t="n">
+        <v>15</v>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Has water in the dry season; very good quality, travellers drink and wash</t>
+          <t>15 L/min</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Handpump had no water in the dry season</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>access</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
+          <t>Dry-season flow after DI.</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8090,41 +8525,37 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>village_change</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+          <t>monsoon_flow_lpm</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>22</v>
+      </c>
+      <c r="J79" t="n">
+        <v>22</v>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Flow has increased</t>
+          <t>22 L/min</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+          <t>Agreed by Rajat (2026-10-24) from the earlier RDI reports (before) and the October 2026 field forms (after)</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Lower spring flow</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>access</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
+          <t>Monsoon flow after DI.</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8134,55 +8565,59 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>WDI-08</t>
+          <t>WDI-07</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>FV26-DI-KUN</t>
+          <t>RDI-SPR-0007</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>before_di_agreed</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>before_di</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>pump_status</t>
+          <t>reported_change</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>defunct</t>
+          <t>increase</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>DI was fitted on a previously defunct handpump</t>
+          <t>Flow compared with 10-20 years ago: More. Nearby houses use this spring; flow has increased</t>
         </is>
       </c>
       <c r="O80" t="inlineStr"/>
@@ -8196,7 +8631,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WDI-08</t>
+          <t>WDI-07</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8206,24 +8641,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>FV26-DI-KUN</t>
+          <t>FV26-DI-KAN</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>after_di</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>pump_status</t>
@@ -8233,7 +8664,7 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>defunct</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8243,12 +8674,12 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Water tapped directly from the handpump</t>
+          <t>People said it has water in the dry season now</t>
         </is>
       </c>
       <c r="O81" t="inlineStr"/>
@@ -8262,7 +8693,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WDI-08</t>
+          <t>WDI-07</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -8272,7 +8703,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>FV26-DI-KUN</t>
+          <t>FV26-DI-KAN</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8287,46 +8718,34 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>village_change</t>
+          <t>pump_status</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Handpump working; water tapped directly</t>
+          <t>working</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>Handpump defunct</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>access</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
+          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8336,7 +8755,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>WDI-09</t>
+          <t>WDI-07</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -8346,43 +8765,51 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SRC028-DI-DUN</t>
+          <t>FV26-DI-KAN</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>before_di_agreed</t>
+          <t>watsan_report</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>before_di</t>
+          <t>after_di</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+          <t>flow_lpm</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>16</v>
+      </c>
+      <c r="J83" t="n">
+        <v>16</v>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>defunct</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>report</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>WATSAN Spring Assessment Report (SRC-003), summary table; date and method not stated</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Report's 'nearby DI handpump at higher elevation'; date and method not stated.</t>
+        </is>
+      </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
     </row>
@@ -8394,7 +8821,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>WDI-09</t>
+          <t>WDI-07</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -8404,12 +8831,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SRC028-DI-DUN</t>
+          <t>FV26-DI-KAN</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>after_di_agreed</t>
+          <t>field_visit_2026_10</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -8417,36 +8844,518 @@
           <t>after_di</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>pump_status</t>
+          <t>village_change</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
+          <t>Has water in the dry season</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Handpump had no water in the dry season</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>OBS-084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>WDI-07</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>handpump</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>FV26-DI-KAN</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>field_visit_2026_10</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Very good quality water; travellers drink and wash here</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Handpump defunct</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>OBS-085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>WDI-07</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>RDI-SPR-0007</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>field_visit_2026_10</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Nearby houses say the flow has increased</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Lower spring flow</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>OBS-086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>WDI-08</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>handpump</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>FV26-DI-KUN</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>before_di_agreed</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>defunct</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>agreed</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>DI was fitted on a previously defunct handpump</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>OBS-087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>WDI-08</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>handpump</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>FV26-DI-KUN</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>field_visit_2026_10</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
           <t>working</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>agreed</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Water tapped directly from the handpump</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>OBS-088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>WDI-08</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>handpump</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>FV26-DI-KUN</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>field_visit_2026_10</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Handpump working; water tapped directly</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Field form, DOCC/WATSAN field visit, October 2026</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Handpump defunct</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>OBS-089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>WDI-09</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>handpump</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>SRC028-DI-DUN</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>before_di_agreed</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>defunct</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>agreed</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>OBS-090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>WDI-09</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>handpump</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>SRC028-DI-DUN</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>after_di_agreed</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>pump_status</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>working</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>agreed</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
         <is>
           <t>Not visited; Working (Rajat, 2026-10-24)</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
+++ b/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
@@ -1846,7 +1846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1982,10 +1982,20 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
+          <t>other_work</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>di_note</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>location_class</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>location_note</t>
         </is>
@@ -2112,12 +2122,18 @@
           <t>Has water in the dry season; water decent, slight iron. Rooftop pipe broken, so the DI line is disconnected.</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Roof pipe broken</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
         <is>
           <t>in_catchment</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
         </is>
@@ -2236,12 +2252,18 @@
           <t>DI tested on the visit. Linked to both Balench and Paniyar Dhar (not verified).</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Tested during visit</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>in_catchment</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
         </is>
@@ -2364,12 +2386,18 @@
           <t>DI line, gutter and filter in good order.</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
         <is>
           <t>in_catchment</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
         </is>
@@ -2494,12 +2522,18 @@
           <t>Handpump broken (possible vehicle damage). First flush not working, filter blocked.</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Pump broken</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
         <is>
           <t>outside</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Geologist found no connection between this handpump and the naula.</t>
         </is>
@@ -2628,10 +2662,20 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
+          <t>Test the handpump water for iron</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>in_catchment</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
         </is>
@@ -2744,10 +2788,20 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
+          <t>Test the handpump water (quality improved, but no lab test yet)</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>house construction</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>in_catchment</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
         </is>
@@ -2862,12 +2916,18 @@
           <t>DI tested on the visit. Linked to both Balench and Paniyar Dhar (not verified).</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Tested during visit</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
         <is>
           <t>in_catchment</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
         </is>
@@ -2988,10 +3048,20 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
+          <t>Clean the roadside DI site (litter, dirty inflow)</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>in_catchment</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
         </is>
@@ -3098,10 +3168,20 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
+          <t>Protect the exposed roof pipes from animals and monkeys</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Working (recent DI on a previously defunct handpump)</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>in_catchment</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
         </is>
@@ -3176,6 +3256,8 @@
       </c>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
+++ b/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
@@ -761,11 +761,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>IMD gridded rain gauges, mean of 2001-2025 (24 years; missing 2012)</t>
+          <t>IMD gridded rain gauges, mean of 2001-2025</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -773,7 +773,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -892,11 +892,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>IMD gridded rain gauges, mean of 2001-2025 (24 years; missing 2012)</t>
+          <t>IMD gridded rain gauges, mean of 2001-2025</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1031,11 +1031,11 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>IMD gridded rain gauges, mean of 2001-2025 (24 years; missing 2012)</t>
+          <t>IMD gridded rain gauges, mean of 2001-2025</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1446</v>
+        <v>1439</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>IMD gridded rain gauges, mean of 2001-2025 (24 years; missing 2012)</t>
+          <t>IMD gridded rain gauges, mean of 2001-2025</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>IMD gridded rain gauges, mean of 2001-2025 (24 years; missing 2012)</t>
+          <t>IMD gridded rain gauges, mean of 2001-2025</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1428,11 +1428,11 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>IMD gridded rain gauges, mean of 2001-2025 (24 years; missing 2012)</t>
+          <t>IMD gridded rain gauges, mean of 2001-2025</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>IMD gridded rain gauges, mean of 2001-2025 (24 years; missing 2012)</t>
+          <t>IMD gridded rain gauges, mean of 2001-2025</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1682,11 +1682,11 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1446</v>
+        <v>1439</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>IMD gridded rain gauges, mean of 2001-2025 (24 years; missing 2012)</t>
+          <t>IMD gridded rain gauges, mean of 2001-2025</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1785,11 +1785,11 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>IMD gridded rain gauges, mean of 2001-2025 (24 years; missing 2012)</t>
+          <t>IMD gridded rain gauges, mean of 2001-2025</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">

--- a/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
+++ b/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
@@ -2249,7 +2249,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>DI tested on the visit. Linked to both Balench and Paniyar Dhar (not verified).</t>
+          <t>DI tested on the visit. Link to both springs not verified yet.</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr"/>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>DI tested on the visit. Linked to both Balench and Paniyar Dhar (not verified).</t>
+          <t>DI tested on the visit. Link to both springs not verified yet.</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr"/>

--- a/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
+++ b/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9 DI springs from the WATSAN Spring Assessment Report and the SRHU reports. Arakot 2 may feed both Balench and Paniyar Dhar, so it is listed under both; count its water once. Kokhliyal is a Himmotthan site without DI, so it is not included.</t>
+          <t>8 DI springs from the WATSAN Spring Assessment Report and the SRHU Badera report. Makhdet (Dungsi) is left out until its DI is installed. Arakot 2 may feed both Balench and Paniyar Dhar, so it is listed under both; count its water once. Kokhliyal is a Himmotthan site without DI, so it is not included.</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,8 +786,12 @@
           <t>19</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>10</v>
+      </c>
+      <c r="S2" t="n">
+        <v>50</v>
+      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>FV26-DI-ARK1;FV26-DI-ARK2</t>
@@ -917,15 +921,11 @@
           <t>39</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="R3" t="n">
+        <v>27</v>
+      </c>
+      <c r="S3" t="n">
+        <v>135</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Families once walked 2-3 km downhill for water. Today all 28 households (about 200 people) have water in the village, and it now supports vegetation and farming. People also report more water in springs further downhill at Silogi. The Himmotthan solar pumping scheme works alongside DI here.</t>
+          <t>Families once walked 2-3 km downhill for water. Today all 27 households (about 135 people) have water in the village, and it now supports vegetation and farming. People also report more water in springs further downhill at Silogi. The Himmotthan solar pumping scheme works alongside DI here.</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1191,8 +1191,12 @@
           <t>29</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>15</v>
+      </c>
+      <c r="S5" t="n">
+        <v>75</v>
+      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>FV26-DI-GUN</t>
@@ -1323,7 +1327,9 @@
           <t>20</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>100</v>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>FV26-DI-CHP2</t>
@@ -1453,8 +1459,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>FV26-DI-ARK2</t>
@@ -1584,8 +1594,12 @@
           <t>131</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>15</v>
+      </c>
+      <c r="S8" t="n">
+        <v>75</v>
+      </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>FV26-DI-KAN</t>
@@ -1707,8 +1721,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>15</v>
+      </c>
+      <c r="S9" t="n">
+        <v>75</v>
+      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>FV26-DI-KUN</t>
@@ -1735,105 +1753,6 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>WDI-09</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>RDI-SPR-0009</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>DI site</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Makhdet</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Makhdet (Dungsi &amp; Makhdet; also spelt Madkhet, Domsi)</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Tehri Garhwal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>30.482739</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>78.234675</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1479.6</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>1330</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>IMD gridded rain gauges, mean of 2001-2025</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>2105</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>71.6</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>232.3</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>SRC028-DI-DUN</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Reported by the SRHU report (SRC-028); not visited</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>91.07</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1846,7 +1765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2065,8 +1984,14 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Rajat, 2026-10-24</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>ok</t>
@@ -2203,8 +2128,14 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Rajat, 2026-10-24</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>ok</t>
@@ -2329,8 +2260,14 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Rajat, 2026-10-24</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>ok</t>
@@ -2468,7 +2405,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Installed last year for the school (field visit, 20 Oct 2026)</t>
+          <t>Installed last year for the school (field visit, 20 Oct 2026; Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -2493,7 +2430,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>connected</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -2519,7 +2456,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Handpump broken (possible vehicle damage). First flush not working, filter blocked.</t>
+          <t>Handpump broken (possible vehicle damage). DI line intact; first flush not working, filter blocked.</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr"/>
@@ -2603,8 +2540,14 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Rajat, 2026-10-24</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>ok</t>
@@ -2737,11 +2680,17 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Rajat, 2026-10-24</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -2783,7 +2732,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Water quality improved: it was red/brown with high iron before DI (no lab test). DI line disconnected during house construction; filter blocked.</t>
+          <t>Water still orange-yellow at the first flush, but it was red before DI, so it is at least diluted now (no lab test). DI line disconnected during house construction; filter blocked.</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -2867,8 +2816,14 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Rajat, 2026-10-24</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>ok</t>
@@ -2993,8 +2948,14 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Rajat, 2026-10-24</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>ok</t>
@@ -3113,12 +3074,20 @@
           <t>189</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>60</v>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Rajat, 2026-10-24</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>not_checked</t>
@@ -3186,78 +3155,6 @@
           <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SRC028-DI-DUN</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>WDI-09</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Dungsi (Domsi)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>30.481472</v>
-      </c>
-      <c r="F11" t="n">
-        <v>78.236694</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>working</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Reported by the SRHU Dungsi &amp; Makhdet report (SRC-028); not visited</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>SRHU Dungsi &amp; Makhdet hydrogeology report (SRC-028); handpump printed as 30°28'53.3"N 78°14'12.1"E</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Not visited; Working (Rajat, 2026-10-24)</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Not visited; from the SRHU report.</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3270,7 +3167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P91"/>
+  <dimension ref="A1:P89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5066,7 +4963,7 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Water available in the village for all 28 households (about 200 people)</t>
+          <t>Water available in the village for all 27 households (about 135 people)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -9318,126 +9215,6 @@
           <t>better</t>
         </is>
       </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>OBS-089</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>WDI-09</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>handpump</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>SRC028-DI-DUN</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>before_di_agreed</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>before_di</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>defunct</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>agreed</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>OBS-090</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>WDI-09</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>handpump</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>SRC028-DI-DUN</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>after_di_agreed</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>after_di</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>pump_status</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>working</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>agreed</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>Not visited; Working (Rajat, 2026-10-24)</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
+++ b/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
@@ -1976,7 +1976,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Form gives 300 m2 for Arakot 1 and 2 together; split evenly</t>
+          <t>150 m2 each for Arakot 1 and 2 (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Form gives 300 m2 for Arakot 1 and 2 together; split evenly</t>
+          <t>150 m2 each for Arakot 1 and 2 (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Form value unclear</t>
+          <t>Form value hard to read; 120 m2 kept (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Form gives 300 m2 for Arakot 1 and 2 together; split evenly</t>
+          <t>150 m2 each for Arakot 1 and 2 (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3077,8 +3077,14 @@
       <c r="J10" t="n">
         <v>60</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>150</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Rajat, 2026-10-24</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
         <v>2026</v>
@@ -3167,7 +3173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P89"/>
+  <dimension ref="A1:P90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9027,52 +9033,48 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>handpump</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>FV26-DI-KUN</t>
+          <t>RDI-SPR-0008</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>before_di_agreed</t>
+          <t>rajat_2026_10_24</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>before_di</t>
+          <t>after_di</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>pump_status</t>
+          <t>flow_lpm</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>defunct</t>
+          <t>Not measured yet: the spring is covered, so there is no access to the outlet</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>not_measured</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>DI was fitted on a previously defunct handpump</t>
-        </is>
-      </c>
+          <t>Rajat, 2026-10-24</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
     </row>
@@ -9099,19 +9101,15 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>field_visit_2026_10</t>
+          <t>before_di_agreed</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>after_di</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
+          <t>before_di</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>pump_status</t>
@@ -9121,7 +9119,7 @@
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>defunct</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -9131,12 +9129,12 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+          <t>All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Water tapped directly from the handpump</t>
+          <t>DI was fitted on a previously defunct handpump</t>
         </is>
       </c>
       <c r="O88" t="inlineStr"/>
@@ -9180,37 +9178,103 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>village_change</t>
+          <t>pump_status</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
+          <t>working</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>agreed</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Field form, DOCC/WATSAN field visit, October 2026; All WATSAN DI handpumps were defunct before DI (Rajat, 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Water tapped directly from the handpump</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>OBS-089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>WDI-08</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>handpump</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>FV26-DI-KUN</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>field_visit_2026_10</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>after_di</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>village_change</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
           <t>Handpump working; water tapped directly</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>Field form, DOCC/WATSAN field visit, October 2026</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>Handpump defunct</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>access</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>better</t>
         </is>

--- a/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
+++ b/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kunjapuri</t>
+          <t>Badeda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Working again; people tap water directly. Exposed roof pipes at risk from animals and monkeys.</t>
+          <t>Most recent DI (2026); filter and first flush clean. Working again; people tap water directly. Exposed roof pipes at risk from animals and monkeys.</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">

--- a/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
+++ b/data/02_processed/watsan_di/watsan_di_sites_v1.xlsx
@@ -2060,7 +2060,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
+          <t>In the surface catchment but outside the top recharge zones: little of the water is likely to reach this spring. (Spring planner, 2026-10-24.)</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>in_catchment</t>
+          <t>outside</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
+          <t>Outside the spring's catchment and its recharge zones: the water will mostly feed other springs or streams. (Spring planner, 2026-10-24.)</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
+          <t>In the surface catchment but outside the top recharge zones: little of the water is likely to reach this spring. (Spring planner, 2026-10-24.)</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
+          <t>In the surface catchment but outside the top recharge zones: little of the water is likely to reach this spring. (Spring planner, 2026-10-24.)</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
+          <t>In the surface catchment but outside the top recharge zones: little of the water is likely to reach this spring. (Spring planner, 2026-10-24.)</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
+          <t>In the surface catchment but outside the top recharge zones: little of the water is likely to reach this spring. (Spring planner, 2026-10-24.)</t>
         </is>
       </c>
     </row>
@@ -3019,12 +3019,12 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>in_catchment</t>
+          <t>in_zone_slope</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
+          <t>Inside recharge zone R1, on the slope that drains to the spring: most of the injected water can reach it. (Spring planner, 2026-10-24.)</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Above the spring with a reported link; the planner's recharge zones are not run for this site yet, so the 'in the catchment' share is used.</t>
+          <t>In the surface catchment but outside the top recharge zones: little of the water is likely to reach this spring. (Spring planner, 2026-10-24.)</t>
         </is>
       </c>
     </row>
